--- a/Data Files/Auto/RenovacoesSantanderData/RenovaSantander.xlsx
+++ b/Data Files/Auto/RenovacoesSantanderData/RenovaSantander.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Ntxnas1.intrallianz.es\brasil\DIRETORIAS\DIR EXE OPERACOES\DIR TI\SUPERINT DESENV PRODUTOS\RPA\Denilson\EXECUÇÃO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{81E719B5-366C-4C5B-836B-CBEB8209B725}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2BAC6C-10BA-41CA-9302-8E279B8B8DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RenovaSantander" r:id="rId1" sheetId="1"/>
-    <sheet name="Cronograma" r:id="rId2" sheetId="2"/>
+    <sheet name="RenovaSantander" sheetId="1" r:id="rId1"/>
+    <sheet name="Cronograma" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">RenovaSantander!$A$1:$AG$2</definedName>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">Cronograma!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RenovaSantander!$A$1:$AG$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Cronograma!$A$1:$C$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
   <si>
     <t>FINAL_VIG</t>
   </si>
@@ -212,9 +212,6 @@
     <t>5177202551312333007</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -236,14 +233,16 @@
     <t>EMISSÃO REALIZADA : 1211-AUTOMÓVEL [780898951]</t>
   </si>
   <si>
-    <t xml:space="preserve">denilson.inmetricsext@allpronet.com.br, andre.antunes@allianz.com.br                                    </t>
+    <t xml:space="preserve">denilson.inmetricsext@allpronet.com.br                           </t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -471,87 +470,87 @@
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="8" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="9" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="9" fillId="6" fontId="5" numFmtId="14" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="9" fillId="6" fontId="5" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="9" fillId="6" fontId="7" numFmtId="14" xfId="0">
+    <xf numFmtId="14" fontId="7" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="9" fillId="6" fontId="7" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="3"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="6" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="7" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="8" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="6" fillId="4" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle builtinId="8" name="Hiperlink" xfId="3"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Hiperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6092E6CE-1D88-4708-8615-617FC051956B}"/>
     <cellStyle name="Normal 2 2" xfId="2" xr:uid="{426011DD-007C-47A0-A052-4AB327CDA7E7}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
       <color rgb="FFFF9393"/>
@@ -575,10 +574,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -613,7 +612,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -665,7 +664,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -776,21 +775,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -807,7 +806,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -859,52 +858,52 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="22.85546875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="15.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="14.85546875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="16.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="24.85546875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" width="37.5703125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="53.85546875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" width="34.42578125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" width="53.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" width="14.42578125" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="22.140625" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="51.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" width="51.0" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="47.85546875" collapsed="true"/>
-    <col min="15" max="16" bestFit="true" customWidth="true" width="11.28515625" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="26.42578125" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" width="26.42578125" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="65.5703125" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="26.7109375" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="23.140625" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="24.85546875" collapsed="true"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="23.140625" collapsed="true"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="24.85546875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="20.140625" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="22.0" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="12.5703125" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="34.5703125" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="25.140625" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="15.42578125" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="29.5703125" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="61.140625" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="48.85546875" collapsed="true"/>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="24.85546875" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="37.5703125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="53.85546875" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="34.42578125" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="53.85546875" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="22.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="51" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="51" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="47.85546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="11.28515625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="26.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="26.42578125" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="65.5703125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="26.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="23.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="24.85546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="23.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="24.85546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="20.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="22" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="12.5703125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="34.5703125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="25.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="15.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="31" max="31" width="29.5703125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="32" max="32" width="61.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="33" max="33" width="48.85546875" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -1015,10 +1014,10 @@
       <c r="B2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
-        <v>58</v>
-      </c>
+      <c r="C2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="10"/>
       <c r="E2" s="10" t="s">
         <v>50</v>
       </c>
@@ -1041,7 +1040,7 @@
         <v>43</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O2" s="10" t="s">
         <v>45</v>
@@ -1062,44 +1061,69 @@
         <v>55</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="V2" s="10"/>
       <c r="W2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="X2" s="10"/>
       <c r="Y2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="10" t="s">
-        <v>58</v>
-      </c>
+      <c r="Z2" s="10"/>
       <c r="AA2" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AB2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AD2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AE2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AF2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AG2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="AG2" s="11" t="s">
-        <v>64</v>
-      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG2" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -1109,37 +1133,37 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink display="denilson.inmetricsext@allpronet.com.br                                        " r:id="rId1" ref="N2" xr:uid="{B3DE2252-BBFD-41ED-96D3-D35027D93843}"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{B3DE2252-BBFD-41ED-96D3-D35027D93843}"/>
   </hyperlinks>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" customWidth="true" width="19.85546875" collapsed="true"/>
+    <col min="1" max="3" width="19.85546875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="15.75" r="1" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="20"/>
     </row>
-    <row ht="15.75" r="2" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>22</v>
       </c>
@@ -1148,7 +1172,7 @@
       </c>
       <c r="C2" s="23"/>
     </row>
-    <row ht="15.75" r="3" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22"/>
       <c r="B3" s="5" t="s">
         <v>24</v>
@@ -1157,7 +1181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row ht="15.75" r="4" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>46327</v>
       </c>
@@ -1168,7 +1192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="5" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>46328</v>
       </c>
@@ -1179,7 +1203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="6" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>46329</v>
       </c>
@@ -1190,55 +1214,55 @@
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="7" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <v>46330</v>
       </c>
       <c r="B7" s="15">
-        <f ref="B7:B31" si="0" t="shared">A7-15</f>
+        <f t="shared" ref="B7:B31" si="0">A7-15</f>
         <v>46315</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="8" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>46331</v>
       </c>
       <c r="B8" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46316</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="15.75" r="9" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>46332</v>
       </c>
       <c r="B9" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46317</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row ht="15.75" r="10" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>46333</v>
       </c>
       <c r="B10" s="15">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46318</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="11" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
         <v>46334</v>
       </c>
@@ -1249,7 +1273,7 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="12" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <v>46335</v>
       </c>
@@ -1260,67 +1284,67 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="13" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>46336</v>
       </c>
       <c r="B13" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46321</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row ht="15.75" r="14" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>46337</v>
       </c>
       <c r="B14" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46322</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="15" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>46338</v>
       </c>
       <c r="B15" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46323</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="15.75" r="16" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>46339</v>
       </c>
       <c r="B16" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46324</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row ht="15.75" r="17" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
         <v>46340</v>
       </c>
       <c r="B17" s="15">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46325</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="18" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <v>46341</v>
       </c>
@@ -1331,7 +1355,7 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="19" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
         <v>46342</v>
       </c>
@@ -1342,7 +1366,7 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="20" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>46343</v>
       </c>
@@ -1353,55 +1377,55 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="21" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>46344</v>
       </c>
       <c r="B21" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46329</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="22" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>46345</v>
       </c>
       <c r="B22" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46330</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="15.75" r="23" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <v>46346</v>
       </c>
       <c r="B23" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46331</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row ht="15.75" r="24" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>46347</v>
       </c>
       <c r="B24" s="15">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46332</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="25" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <v>46348</v>
       </c>
@@ -1412,7 +1436,7 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="26" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <v>46349</v>
       </c>
@@ -1423,67 +1447,67 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="27" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12">
         <v>46350</v>
       </c>
       <c r="B27" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46335</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row ht="15.75" r="28" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <v>46351</v>
       </c>
       <c r="B28" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46336</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row ht="15.75" r="29" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12">
         <v>46352</v>
       </c>
       <c r="B29" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46337</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="15.75" r="30" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
         <v>46353</v>
       </c>
       <c r="B30" s="12">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46338</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row ht="15.75" r="31" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
         <v>46354</v>
       </c>
       <c r="B31" s="15">
-        <f si="0" t="shared"/>
+        <f t="shared" si="0"/>
         <v>46339</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="32" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
         <v>46355</v>
       </c>
@@ -1494,7 +1518,7 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="15.75" r="33" spans="1:3" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
         <v>46356</v>
       </c>
@@ -1513,12 +1537,12 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
